--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -154,9 +154,6 @@
     <t>Develop</t>
   </si>
   <si>
-    <t>C:\Users\anwar\OneDrive\Documents\UiPath\User Data Extraction and Validation\Data\Output\Output.xlsx</t>
-  </si>
-  <si>
     <t>OutputFile</t>
   </si>
   <si>
@@ -179,6 +176,9 @@
   </si>
   <si>
     <t>Employment</t>
+  </si>
+  <si>
+    <t>Data\Output\Output.xlsx</t>
   </si>
 </sst>
 </file>
@@ -550,7 +550,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -618,7 +618,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>21</v>
@@ -634,34 +634,34 @@
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" t="s">
         <v>47</v>
-      </c>
-      <c r="B6" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
         <v>45</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
